--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/national-income-saving-employment/Institutional Sector-Wise Gross Capital Formation (At Current Prices) (Base Year _ 2011-12).xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/national-income-saving-employment/Institutional Sector-Wise Gross Capital Formation (At Current Prices) (Base Year _ 2011-12).xlsx
@@ -299,9 +299,9 @@
     <t>Base Year : 2011-12</t>
   </si>
   <si>
-    <t xml:space="preserve">NPISH  : Non- profit institutions serving households.
-Notes   : Items 1 to 6 excludes valuables and errors &amp; omissions.
-Source : National Statistical Office (NSO).</t>
+    <t xml:space="preserve">Notes  :  1. NPISH: Non-profit institutions serving households.
+              2. Items 1 to 6 exclude valuables and errors &amp; omissions.
+Source : National Statistics Office (NSO).</t>
   </si>
 </sst>
 </file>
@@ -2907,7 +2907,7 @@
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="24" s="1" customFormat="1" ht="41.5974" customHeight="1">
+    <row r="24" s="1" customFormat="1" ht="31.4647" customHeight="1">
       <c r="B24" s="14" t="s">
         <v>95</v>
       </c>
